--- a/testcases/corporate-pricing/corporate-pricing-loc-import.xlsx
+++ b/testcases/corporate-pricing/corporate-pricing-loc-import.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1188,12 +1188,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TC-CPR-LIM-008</t>
+          <t xml:space="preserve">TC-CPR-LIM-008</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Loc Pricing Import - full/large-file boundary (verified-live 500 replace-failure; not safely automatable)</t>
+          <t>Loc Pricing Import rejects a header-only CSV (headers, zero data rows) in the browser and runs no import</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1207,67 +1207,6 @@
         </is>
       </c>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Pending Automation</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>On the Search screen</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>1. (Not automated) Import the full ~38k-row exported file</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>The full ~38,000-row import fails server-side. The upload stalls part-way through - the dialog progress bar stops near the middle and shows *"Import failed due to a server error. Please try again. If the problem continues, contact support."* The underlying request returns HTTP 500 with a *"Failed to replace... document..."* body - a server-side replace failure, not a gateway timeout. Because the file is re-imported unchanged, no location's values change: office 5897's rows and the total exported row count are identical afterward</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TC-CPR-LIM-009</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Loc Pricing Import rejects a header-only CSV (headers, zero data rows) in the browser and runs no import</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>corporate-pricing</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>loc_pricing_import</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
@@ -1275,264 +1214,264 @@
 Sample input 1: "Loc Pricing Import"</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>On the Search screen (office 1604)</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1. Open "Loc Pricing Import" and attach a CSV that has the 11 header columns but no data rows.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>The Loc Pricing Import dialog opens and the file is attached for upload.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1. Open "Loc Pricing Import" and attach a CSV that has the 11 header columns but no data rows.</t>
+          <t>2. Observe the dialog and whether any import request fires</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>The Loc Pricing Import dialog opens and the file is attached for upload.</t>
+          <t>The dialog shows "Please check the upload file format.", no import request is sent, and office 5897 is unchanged. This is a DISTINCT input from the zero-byte empty file (TC-CPR-LIM-003) - a header-only file is a separate rejection path with its own message</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2. Observe the dialog and whether any import request fires</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>The dialog shows "Please check the upload file format.", no import request is sent, and office 5897 is unchanged. This is a DISTINCT input from the zero-byte empty file (TC-CPR-LIM-003) - a header-only file is a separate rejection path with its own message</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TC-CPR-LIM-010</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-CPR-LIM-009</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Loc Pricing Import applies only the Alternate flag — Internal/Labor/Production columns are not written</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>corporate-pricing</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>loc_pricing_import</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>On the Search screen (office 1604). Office 5897 reset to its baseline first</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1. Upload a single-location file that sets ALL FOUR boolean flag columns (IsInternal, IsLabor, IsAlternate, IsProduction) to 1 on one pricebook row.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>The dialog accepts the file and the import completes successfully.</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1. Upload a single-location file that sets ALL FOUR boolean flag columns (IsInternal, IsLabor, IsAlternate, IsProduction) to 1 on one pricebook row.</t>
+          <t>2. Re-download the export and read that row</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>The dialog accepts the file and the import completes successfully.</t>
+          <t>The import returns HTTP 200 success, but the fresh export shows ONLY IsAlternate changed to 1 - IsInternal, IsLabor, and IsProduction stay 0. Of the flag columns, only IsAlternate is applied by the import</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2. Re-download the export and read that row</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>The import returns HTTP 200 success, but the fresh export shows ONLY IsAlternate changed to 1 - IsInternal, IsLabor, and IsProduction stay 0. Of the flag columns, only IsAlternate is applied by the import</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TC-CPR-LIM-011</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-CPR-LIM-010</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Loc Pricing Import silently drops a pricebook not already defined in the system — no row is created</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>corporate-pricing</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>loc_pricing_import</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>On the Search screen (office 1604). Office 5897 reset to its baseline first</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1. Upload a file containing office 5897's three baseline rows PLUS one row for a novel pricebook name that does not exist in the system.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>The dialog accepts the file and the import completes successfully.</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1. Upload a file containing office 5897's three baseline rows PLUS one row for a novel pricebook name that does not exist in the system.</t>
+          <t>2. Read the import response body and re-download the export</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>The dialog accepts the file and the import completes successfully.</t>
+          <t>The import returns success but the response's createdCount is 0, and the novel pricebook does NOT appear in the re-downloaded export - office 5897 still has exactly its three baseline rows. The import updates existing pricebooks; it does not create a new pricebook definition</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2. Read the import response body and re-download the export</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>The import returns success but the response's createdCount is 0, and the novel pricebook does NOT appear in the re-downloaded export - office 5897 still has exactly its three baseline rows. The import updates existing pricebooks; it does not create a new pricebook definition</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TC-CPR-LIM-012</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-CPR-LIM-011</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Loc Pricing Import opens the "Import All Location Pricing" dialog</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>corporate-pricing</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>loc_pricing_import</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
@@ -1540,39 +1479,62 @@
 Sample input 1: "Loc Pricing Import"</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>On the Search screen with the grid loaded (office 1604)</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1. Click "Loc Pricing Import" (a direct button, not a menu variant)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>The "Import All Location Pricing" dialog opens.</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1. Click "Loc Pricing Import" (a direct button, not a menu variant)</t>
+          <t>2. Read the dialog</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>The "Import All Location Pricing" dialog opens.</t>
+          <t>The dialog displays an upload control and an Upload button for selecting a file.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -1590,70 +1552,47 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2. Read the dialog</t>
+          <t>3. Close the dialog (no file uploaded)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>The dialog displays an upload control and an Upload button for selecting a file.</t>
+          <t>Loc Pricing Import opens the "Import All Location Pricing" upload dialog (a direct trigger, distinct from the grid Import ▾ variants; the real upload round-trip is covered by TC-CPR-LIM-001..011)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>3. Close the dialog (no file uploaded)</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Loc Pricing Import opens the "Import All Location Pricing" upload dialog (a direct trigger, distinct from the grid Import ▾ variants; the real upload round-trip is covered by TC-CPR-LIM-001..011)</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Corporate Pricing — Loc Pricing Import</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Automated: 11 / Pending: 1</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automated: 11 / Pending: 0</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Pass:11 Fail:0 Skipped:0 Blocked:0</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>Last Updated: 2026-08-12</t>
         </is>
